--- a/owlcms/src/main/resources/templates/teams/VFE_Teams-A4.xlsx
+++ b/owlcms/src/main/resources/templates/teams/VFE_Teams-A4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms4\owlcms\src\main\resources\templates\teams\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C35E41-FA68-418D-92C8-FA36246C5813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6225011F-F16A-4B34-A29E-E8CE327A40D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5655" yWindow="2955" windowWidth="22410" windowHeight="15555" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6000" yWindow="3300" windowWidth="22410" windowHeight="15555" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team List" sheetId="3" r:id="rId1"/>
@@ -977,7 +977,7 @@
     <col min="2" max="2" width="8.5703125" customWidth="1"/>
     <col min="3" max="3" width="30.5703125" customWidth="1"/>
     <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="1.42578125" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="2.42578125" style="1" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="12.28515625" style="1" customWidth="1"/>
     <col min="7" max="7" width="10.42578125" style="1" customWidth="1"/>
     <col min="8" max="11" width="11.140625" style="2" customWidth="1"/>

--- a/owlcms/src/main/resources/templates/teams/VFE_Teams-A4.xlsx
+++ b/owlcms/src/main/resources/templates/teams/VFE_Teams-A4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms4\owlcms\src\main\resources\templates\teams\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6225011F-F16A-4B34-A29E-E8CE327A40D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84B9889-3FDD-4A92-ABE6-B31D6032E8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6000" yWindow="3300" windowWidth="22410" windowHeight="15555" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
     <definedName name="dernier">#REF!</definedName>
     <definedName name="essais">#REF!</definedName>
     <definedName name="essaisArr">#REF!</definedName>
-    <definedName name="Excel_BuiltIn__FilterDatabase" localSheetId="0">'Team List'!$A$7:$M$8</definedName>
+    <definedName name="Excel_BuiltIn__FilterDatabase" localSheetId="0">'Team List'!$A$6:$K$7</definedName>
     <definedName name="Excel_BuiltIn_Criteria_1">#REF!</definedName>
     <definedName name="GroupeCourant">#REF!</definedName>
     <definedName name="Groupes">#REF!</definedName>
@@ -47,7 +47,7 @@
     <definedName name="P_C_">#REF!</definedName>
     <definedName name="PeséeGroupFilter">#REF!</definedName>
     <definedName name="PRÉNOM">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Team List'!$A:$H</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Team List'!$A:$F</definedName>
     <definedName name="progr_">#REF!</definedName>
     <definedName name="requestedCJ">#REF!</definedName>
     <definedName name="StartGroupFilter">#REF!</definedName>
@@ -83,7 +83,7 @@
             <family val="2"/>
           </rPr>
           <t>jx:area(lastCell="AA16")
-jx:each(items="lifters" var="group" groupBy="team" groupOrder="ASC" multisheet="group.item.team" lastCell="AA16")</t>
+jx:each(items="lifters" var="group" groupBy="team" groupOrder="ASC" multisheet="group.item.team" lastCell="J16")</t>
         </r>
       </text>
     </comment>
@@ -96,8 +96,8 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>jx:each(items="group.items" var="l" varIndex="lIndex" select="l.gender == 'F'" lastCell="AA11")
-jx:if(condition="lIndex == 0" lastCell="AA10")</t>
+          <t>jx:each(items="group.items" var="l" varIndex="lIndex" select="l.gender == 'F'" lastCell="J11")
+jx:if(condition="lIndex == 0" lastCell="J10")</t>
         </r>
       </text>
     </comment>
@@ -110,8 +110,8 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>jx:each(items="group.items" var="l" varIndex="lIndex" select="l.gender == 'M'" lastCell="AA14")
-jx:if(condition="lIndex == 0" lastCell="AA13")</t>
+          <t>jx:each(items="group.items" var="l" varIndex="lIndex" select="l.gender == 'M'" lastCell="J14")
+jx:if(condition="lIndex == 0" lastCell="J13")</t>
         </r>
       </text>
     </comment>
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="31">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -137,9 +137,6 @@
     <t>${competition.competitionSite}</t>
   </si>
   <si>
-    <t xml:space="preserve"> ${t.get("Competition.competitionCity")} : </t>
-  </si>
-  <si>
     <t>${competition.competitionCity}</t>
   </si>
   <si>
@@ -149,9 +146,6 @@
     <t>${competition.competitionDate}</t>
   </si>
   <si>
-    <t xml:space="preserve">${t.get("Competition.competitionOrganizer")} : </t>
-  </si>
-  <si>
     <t>${competition.competitionOrganizer}</t>
   </si>
   <si>
@@ -161,9 +155,6 @@
     <t>${t.get("FirstName")}</t>
   </si>
   <si>
-    <t>M/F</t>
-  </si>
-  <si>
     <t>${t.get("Results.Birth")}</t>
   </si>
   <si>
@@ -179,9 +170,6 @@
     <t>${l.firstName}</t>
   </si>
   <si>
-    <t>${l.club}</t>
-  </si>
-  <si>
     <t>${t.get("Gender")}</t>
   </si>
   <si>
@@ -212,22 +200,19 @@
     <t>${t.get("Change")}</t>
   </si>
   <si>
-    <t>${t.get("Team")}</t>
-  </si>
-  <si>
     <t>${t.get("Gender.Men")}</t>
   </si>
   <si>
     <t>${t.get("Gender.Women")}</t>
   </si>
   <si>
-    <t>${masters ? l.mastersLongRegistrationCategoryName : l.registrationCategory}</t>
-  </si>
-  <si>
     <t>VFE</t>
   </si>
   <si>
     <t>${t.get("Jury.Signature")}</t>
+  </si>
+  <si>
+    <t>${l.categoryName}</t>
   </si>
 </sst>
 </file>
@@ -240,7 +225,7 @@
     <numFmt numFmtId="166" formatCode="0;\(0\);\-"/>
     <numFmt numFmtId="167" formatCode="_-#,##0;[Red]\(#,##0\);\-"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -292,20 +277,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Arial"/>
@@ -334,8 +305,27 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -354,14 +344,8 @@
         <bgColor indexed="31"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="26"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -430,20 +414,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -460,14 +435,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -475,9 +444,6 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -510,19 +476,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -533,14 +493,7 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
@@ -554,10 +507,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -568,17 +518,33 @@
     </xf>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -586,13 +552,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -970,33 +936,31 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA108"/>
+  <dimension ref="A1:Y108"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.85546875" customWidth="1"/>
     <col min="2" max="2" width="8.5703125" customWidth="1"/>
     <col min="3" max="3" width="30.5703125" customWidth="1"/>
     <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="2.42578125" style="1" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" style="1" customWidth="1"/>
-    <col min="8" max="11" width="11.140625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="23.85546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="16.28515625" style="3" customWidth="1"/>
-    <col min="14" max="15" width="7.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="7.7109375" customWidth="1"/>
-    <col min="17" max="17" width="7.7109375" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9.7109375" style="1" customWidth="1"/>
-    <col min="19" max="20" width="7.7109375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="7.7109375" customWidth="1"/>
-    <col min="22" max="23" width="7.7109375" style="1" customWidth="1"/>
-    <col min="24" max="24" width="6.28515625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="4.140625" style="1" customWidth="1"/>
-    <col min="26" max="26" width="8.140625" style="1" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="1" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="1" customWidth="1"/>
+    <col min="6" max="9" width="11.140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="23.85546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" style="3" customWidth="1"/>
+    <col min="12" max="13" width="7.7109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7109375" customWidth="1"/>
+    <col min="15" max="15" width="7.7109375" style="4" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" style="1" customWidth="1"/>
+    <col min="17" max="18" width="7.7109375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.7109375" customWidth="1"/>
+    <col min="20" max="21" width="7.7109375" style="1" customWidth="1"/>
+    <col min="22" max="22" width="6.28515625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="4.140625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="8.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1009,13 +973,13 @@
       <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -1027,1683 +991,1646 @@
       <c r="J1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="4"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1"/>
-      <c r="U1" s="1"/>
+      <c r="L1" s="4"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1"/>
+      <c r="S1" s="1"/>
+      <c r="V1"/>
+      <c r="W1"/>
       <c r="X1"/>
-      <c r="Y1"/>
-      <c r="Z1"/>
-    </row>
-    <row r="2" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="N2" s="4"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2"/>
-      <c r="U2" s="1"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="L2" s="4"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2"/>
+      <c r="S2" s="1"/>
+      <c r="V2"/>
+      <c r="W2"/>
       <c r="X2"/>
-      <c r="Y2"/>
-      <c r="Z2"/>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="6" t="s">
+      <c r="D3" s="6"/>
+      <c r="E3" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="N3" s="4"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3"/>
-      <c r="U3" s="1"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="L3" s="4"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3"/>
+      <c r="S3" s="1"/>
+      <c r="V3"/>
+      <c r="W3"/>
       <c r="X3"/>
-      <c r="Y3"/>
-      <c r="Z3"/>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="8"/>
+      <c r="E4" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="L4" s="4"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4"/>
+      <c r="S4" s="1"/>
+      <c r="V4"/>
+      <c r="W4"/>
+      <c r="X4"/>
+    </row>
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+    </row>
+    <row r="6" spans="1:24" s="20" customFormat="1" ht="21.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="19"/>
+    </row>
+    <row r="7" spans="1:24" s="43" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="38"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="42"/>
+      <c r="T7" s="42"/>
+      <c r="U7" s="42"/>
+      <c r="V7" s="42"/>
+      <c r="W7" s="42"/>
+      <c r="X7" s="42"/>
+    </row>
+    <row r="8" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="50" t="s">
+      <c r="D8" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="N4" s="4"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4"/>
-      <c r="U4" s="1"/>
-      <c r="X4"/>
-      <c r="Y4"/>
-      <c r="Z4"/>
-    </row>
-    <row r="5" spans="1:26" s="12" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="51" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15"/>
-      <c r="U5" s="15"/>
-      <c r="V5" s="15"/>
-      <c r="W5" s="15"/>
-    </row>
-    <row r="6" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
+      <c r="E8" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="15"/>
+    </row>
+    <row r="9" spans="1:24" s="23" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="22"/>
+    </row>
+    <row r="10" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="19"/>
+    </row>
+    <row r="11" spans="1:24" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="16" t="s">
+      <c r="F11" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="33"/>
+      <c r="J11" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="17"/>
+      <c r="M11"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="1"/>
+      <c r="R11"/>
+      <c r="S11" s="1"/>
+      <c r="X11"/>
+    </row>
+    <row r="12" spans="1:24" s="23" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="22"/>
+    </row>
+    <row r="13" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="19"/>
+    </row>
+    <row r="14" spans="1:24" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="C14" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="17" t="s">
+      <c r="G14" s="33"/>
+      <c r="H14" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="33"/>
+      <c r="J14" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="17"/>
+      <c r="M14"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="1"/>
+      <c r="R14"/>
+      <c r="S14" s="1"/>
+      <c r="X14"/>
+    </row>
+    <row r="15" spans="1:24" s="20" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="16"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="19"/>
+    </row>
+    <row r="16" spans="1:24" s="20" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6" s="18"/>
-    </row>
-    <row r="7" spans="1:26" s="23" customFormat="1" ht="21.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="20"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="22"/>
-    </row>
-    <row r="8" spans="1:26" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="19"/>
-    </row>
-    <row r="9" spans="1:26" s="28" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="27"/>
-    </row>
-    <row r="10" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="22"/>
-    </row>
-    <row r="11" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" s="41"/>
-      <c r="J11" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="K11" s="41"/>
-      <c r="L11" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="M11" s="20"/>
-      <c r="O11"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="1"/>
-      <c r="T11"/>
-      <c r="U11" s="1"/>
-      <c r="Z11"/>
-    </row>
-    <row r="12" spans="1:26" s="28" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="26"/>
-      <c r="O12" s="27"/>
-    </row>
-    <row r="13" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="22"/>
-    </row>
-    <row r="14" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="31"/>
-      <c r="F14" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="K14" s="41"/>
-      <c r="L14" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="M14" s="20"/>
-      <c r="O14"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="1"/>
-      <c r="T14"/>
-      <c r="U14" s="1"/>
-      <c r="Z14"/>
-    </row>
-    <row r="15" spans="1:26" s="23" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="22"/>
-    </row>
-    <row r="16" spans="1:26" s="23" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="49" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="21"/>
-      <c r="O16" s="22"/>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="19"/>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19"/>
       <c r="B19"/>
       <c r="C19"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="M19" s="3"/>
-      <c r="P19"/>
-      <c r="Q19" s="4"/>
-      <c r="U19"/>
-      <c r="AA19"/>
-    </row>
-    <row r="20" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K19" s="3"/>
+      <c r="N19"/>
+      <c r="O19" s="4"/>
+      <c r="S19"/>
+      <c r="Y19"/>
+    </row>
+    <row r="20" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="B20"/>
       <c r="C20"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="M20" s="3"/>
-      <c r="P20"/>
-      <c r="Q20" s="4"/>
-      <c r="U20"/>
-      <c r="AA20"/>
-    </row>
-    <row r="21" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K20" s="3"/>
+      <c r="N20"/>
+      <c r="O20" s="4"/>
+      <c r="S20"/>
+      <c r="Y20"/>
+    </row>
+    <row r="21" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="B21"/>
       <c r="C21"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="M21" s="3"/>
-      <c r="P21"/>
-      <c r="Q21" s="4"/>
-      <c r="U21"/>
-      <c r="AA21"/>
-    </row>
-    <row r="22" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K21" s="3"/>
+      <c r="N21"/>
+      <c r="O21" s="4"/>
+      <c r="S21"/>
+      <c r="Y21"/>
+    </row>
+    <row r="22" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="M22" s="3"/>
-      <c r="P22"/>
-      <c r="Q22" s="4"/>
-      <c r="U22"/>
-      <c r="AA22"/>
-    </row>
-    <row r="23" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K22" s="3"/>
+      <c r="N22"/>
+      <c r="O22" s="4"/>
+      <c r="S22"/>
+      <c r="Y22"/>
+    </row>
+    <row r="23" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="B23"/>
       <c r="C23"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="M23" s="3"/>
-      <c r="P23"/>
-      <c r="Q23" s="4"/>
-      <c r="U23"/>
-      <c r="AA23"/>
-    </row>
-    <row r="24" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K23" s="3"/>
+      <c r="N23"/>
+      <c r="O23" s="4"/>
+      <c r="S23"/>
+      <c r="Y23"/>
+    </row>
+    <row r="24" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
       <c r="B24"/>
       <c r="C24"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="M24" s="3"/>
-      <c r="P24"/>
-      <c r="Q24" s="4"/>
-      <c r="U24"/>
-      <c r="AA24"/>
-    </row>
-    <row r="25" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K24" s="3"/>
+      <c r="N24"/>
+      <c r="O24" s="4"/>
+      <c r="S24"/>
+      <c r="Y24"/>
+    </row>
+    <row r="25" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="B25"/>
       <c r="C25"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="M25" s="3"/>
-      <c r="P25"/>
-      <c r="Q25" s="4"/>
-      <c r="U25"/>
-      <c r="AA25"/>
-    </row>
-    <row r="26" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K25" s="3"/>
+      <c r="N25"/>
+      <c r="O25" s="4"/>
+      <c r="S25"/>
+      <c r="Y25"/>
+    </row>
+    <row r="26" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
       <c r="B26"/>
       <c r="C26"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="M26" s="3"/>
-      <c r="P26"/>
-      <c r="Q26" s="4"/>
-      <c r="U26"/>
-      <c r="AA26"/>
-    </row>
-    <row r="27" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K26" s="3"/>
+      <c r="N26"/>
+      <c r="O26" s="4"/>
+      <c r="S26"/>
+      <c r="Y26"/>
+    </row>
+    <row r="27" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
       <c r="B27"/>
       <c r="C27"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="M27" s="3"/>
-      <c r="P27"/>
-      <c r="Q27" s="4"/>
-      <c r="U27"/>
-      <c r="AA27"/>
-    </row>
-    <row r="28" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K27" s="3"/>
+      <c r="N27"/>
+      <c r="O27" s="4"/>
+      <c r="S27"/>
+      <c r="Y27"/>
+    </row>
+    <row r="28" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
       <c r="B28"/>
       <c r="C28"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="M28" s="3"/>
-      <c r="P28"/>
-      <c r="Q28" s="4"/>
-      <c r="U28"/>
-      <c r="AA28"/>
-    </row>
-    <row r="29" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K28" s="3"/>
+      <c r="N28"/>
+      <c r="O28" s="4"/>
+      <c r="S28"/>
+      <c r="Y28"/>
+    </row>
+    <row r="29" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
       <c r="B29"/>
       <c r="C29"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="M29" s="3"/>
-      <c r="P29"/>
-      <c r="Q29" s="4"/>
-      <c r="U29"/>
-      <c r="AA29"/>
-    </row>
-    <row r="30" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K29" s="3"/>
+      <c r="N29"/>
+      <c r="O29" s="4"/>
+      <c r="S29"/>
+      <c r="Y29"/>
+    </row>
+    <row r="30" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="B30"/>
       <c r="C30"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="M30" s="3"/>
-      <c r="P30"/>
-      <c r="Q30" s="4"/>
-      <c r="U30"/>
-      <c r="AA30"/>
-    </row>
-    <row r="31" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K30" s="3"/>
+      <c r="N30"/>
+      <c r="O30" s="4"/>
+      <c r="S30"/>
+      <c r="Y30"/>
+    </row>
+    <row r="31" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
       <c r="B31"/>
       <c r="C31"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="M31" s="3"/>
-      <c r="P31"/>
-      <c r="Q31" s="4"/>
-      <c r="U31"/>
-      <c r="AA31"/>
-    </row>
-    <row r="32" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K31" s="3"/>
+      <c r="N31"/>
+      <c r="O31" s="4"/>
+      <c r="S31"/>
+      <c r="Y31"/>
+    </row>
+    <row r="32" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
       <c r="B32"/>
       <c r="C32"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="M32" s="3"/>
-      <c r="P32"/>
-      <c r="Q32" s="4"/>
-      <c r="U32"/>
-      <c r="AA32"/>
-    </row>
-    <row r="33" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K32" s="3"/>
+      <c r="N32"/>
+      <c r="O32" s="4"/>
+      <c r="S32"/>
+      <c r="Y32"/>
+    </row>
+    <row r="33" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
       <c r="B33"/>
       <c r="C33"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="M33" s="3"/>
-      <c r="P33"/>
-      <c r="Q33" s="4"/>
-      <c r="U33"/>
-      <c r="AA33"/>
-    </row>
-    <row r="34" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K33" s="3"/>
+      <c r="N33"/>
+      <c r="O33" s="4"/>
+      <c r="S33"/>
+      <c r="Y33"/>
+    </row>
+    <row r="34" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="B34"/>
       <c r="C34"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="M34" s="3"/>
-      <c r="P34"/>
-      <c r="Q34" s="4"/>
-      <c r="U34"/>
-      <c r="AA34"/>
-    </row>
-    <row r="35" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K34" s="3"/>
+      <c r="N34"/>
+      <c r="O34" s="4"/>
+      <c r="S34"/>
+      <c r="Y34"/>
+    </row>
+    <row r="35" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="B35"/>
       <c r="C35"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="M35" s="3"/>
-      <c r="P35"/>
-      <c r="Q35" s="4"/>
-      <c r="U35"/>
-      <c r="AA35"/>
-    </row>
-    <row r="36" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K35" s="3"/>
+      <c r="N35"/>
+      <c r="O35" s="4"/>
+      <c r="S35"/>
+      <c r="Y35"/>
+    </row>
+    <row r="36" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="B36"/>
       <c r="C36"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="M36" s="3"/>
-      <c r="P36"/>
-      <c r="Q36" s="4"/>
-      <c r="U36"/>
-      <c r="AA36"/>
-    </row>
-    <row r="37" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K36" s="3"/>
+      <c r="N36"/>
+      <c r="O36" s="4"/>
+      <c r="S36"/>
+      <c r="Y36"/>
+    </row>
+    <row r="37" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="B37"/>
       <c r="C37"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="M37" s="3"/>
-      <c r="P37"/>
-      <c r="Q37" s="4"/>
-      <c r="U37"/>
-      <c r="AA37"/>
-    </row>
-    <row r="38" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K37" s="3"/>
+      <c r="N37"/>
+      <c r="O37" s="4"/>
+      <c r="S37"/>
+      <c r="Y37"/>
+    </row>
+    <row r="38" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="B38"/>
       <c r="C38"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="M38" s="3"/>
-      <c r="P38"/>
-      <c r="Q38" s="4"/>
-      <c r="U38"/>
-      <c r="AA38"/>
-    </row>
-    <row r="39" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K38" s="3"/>
+      <c r="N38"/>
+      <c r="O38" s="4"/>
+      <c r="S38"/>
+      <c r="Y38"/>
+    </row>
+    <row r="39" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="B39"/>
       <c r="C39"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="M39" s="3"/>
-      <c r="P39"/>
-      <c r="Q39" s="4"/>
-      <c r="U39"/>
-      <c r="AA39"/>
-    </row>
-    <row r="40" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K39" s="3"/>
+      <c r="N39"/>
+      <c r="O39" s="4"/>
+      <c r="S39"/>
+      <c r="Y39"/>
+    </row>
+    <row r="40" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="B40"/>
       <c r="C40"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="M40" s="3"/>
-      <c r="P40"/>
-      <c r="Q40" s="4"/>
-      <c r="U40"/>
-      <c r="AA40"/>
-    </row>
-    <row r="41" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K40" s="3"/>
+      <c r="N40"/>
+      <c r="O40" s="4"/>
+      <c r="S40"/>
+      <c r="Y40"/>
+    </row>
+    <row r="41" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="B41"/>
       <c r="C41"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="M41" s="3"/>
-      <c r="P41"/>
-      <c r="Q41" s="4"/>
-      <c r="U41"/>
-      <c r="AA41"/>
-    </row>
-    <row r="42" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K41" s="3"/>
+      <c r="N41"/>
+      <c r="O41" s="4"/>
+      <c r="S41"/>
+      <c r="Y41"/>
+    </row>
+    <row r="42" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="B42"/>
       <c r="C42"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
-      <c r="M42" s="3"/>
-      <c r="P42"/>
-      <c r="Q42" s="4"/>
-      <c r="U42"/>
-      <c r="AA42"/>
-    </row>
-    <row r="43" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K42" s="3"/>
+      <c r="N42"/>
+      <c r="O42" s="4"/>
+      <c r="S42"/>
+      <c r="Y42"/>
+    </row>
+    <row r="43" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="B43"/>
       <c r="C43"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="M43" s="3"/>
-      <c r="P43"/>
-      <c r="Q43" s="4"/>
-      <c r="U43"/>
-      <c r="AA43"/>
-    </row>
-    <row r="44" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K43" s="3"/>
+      <c r="N43"/>
+      <c r="O43" s="4"/>
+      <c r="S43"/>
+      <c r="Y43"/>
+    </row>
+    <row r="44" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44"/>
       <c r="B44"/>
       <c r="C44"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="M44" s="3"/>
-      <c r="P44"/>
-      <c r="Q44" s="4"/>
-      <c r="U44"/>
-      <c r="AA44"/>
-    </row>
-    <row r="45" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K44" s="3"/>
+      <c r="N44"/>
+      <c r="O44" s="4"/>
+      <c r="S44"/>
+      <c r="Y44"/>
+    </row>
+    <row r="45" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="B45"/>
       <c r="C45"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="M45" s="3"/>
-      <c r="P45"/>
-      <c r="Q45" s="4"/>
-      <c r="U45"/>
-      <c r="AA45"/>
-    </row>
-    <row r="46" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K45" s="3"/>
+      <c r="N45"/>
+      <c r="O45" s="4"/>
+      <c r="S45"/>
+      <c r="Y45"/>
+    </row>
+    <row r="46" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="B46"/>
       <c r="C46"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="M46" s="3"/>
-      <c r="P46"/>
-      <c r="Q46" s="4"/>
-      <c r="U46"/>
-      <c r="AA46"/>
-    </row>
-    <row r="47" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K46" s="3"/>
+      <c r="N46"/>
+      <c r="O46" s="4"/>
+      <c r="S46"/>
+      <c r="Y46"/>
+    </row>
+    <row r="47" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47"/>
       <c r="B47"/>
       <c r="C47"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="M47" s="3"/>
-      <c r="P47"/>
-      <c r="Q47" s="4"/>
-      <c r="U47"/>
-      <c r="AA47"/>
-    </row>
-    <row r="48" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K47" s="3"/>
+      <c r="N47"/>
+      <c r="O47" s="4"/>
+      <c r="S47"/>
+      <c r="Y47"/>
+    </row>
+    <row r="48" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="B48"/>
       <c r="C48"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-      <c r="M48" s="3"/>
-      <c r="P48"/>
-      <c r="Q48" s="4"/>
-      <c r="U48"/>
-      <c r="AA48"/>
-    </row>
-    <row r="49" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K48" s="3"/>
+      <c r="N48"/>
+      <c r="O48" s="4"/>
+      <c r="S48"/>
+      <c r="Y48"/>
+    </row>
+    <row r="49" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49"/>
       <c r="B49"/>
       <c r="C49"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-      <c r="M49" s="3"/>
-      <c r="P49"/>
-      <c r="Q49" s="4"/>
-      <c r="U49"/>
-      <c r="AA49"/>
-    </row>
-    <row r="50" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K49" s="3"/>
+      <c r="N49"/>
+      <c r="O49" s="4"/>
+      <c r="S49"/>
+      <c r="Y49"/>
+    </row>
+    <row r="50" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
       <c r="B50"/>
       <c r="C50"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="M50" s="3"/>
-      <c r="P50"/>
-      <c r="Q50" s="4"/>
-      <c r="U50"/>
-      <c r="AA50"/>
-    </row>
-    <row r="51" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K50" s="3"/>
+      <c r="N50"/>
+      <c r="O50" s="4"/>
+      <c r="S50"/>
+      <c r="Y50"/>
+    </row>
+    <row r="51" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51"/>
       <c r="B51"/>
       <c r="C51"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-      <c r="M51" s="3"/>
-      <c r="P51"/>
-      <c r="Q51" s="4"/>
-      <c r="U51"/>
-      <c r="AA51"/>
-    </row>
-    <row r="52" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K51" s="3"/>
+      <c r="N51"/>
+      <c r="O51" s="4"/>
+      <c r="S51"/>
+      <c r="Y51"/>
+    </row>
+    <row r="52" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52"/>
       <c r="B52"/>
       <c r="C52"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-      <c r="M52" s="3"/>
-      <c r="P52"/>
-      <c r="Q52" s="4"/>
-      <c r="U52"/>
-      <c r="AA52"/>
-    </row>
-    <row r="53" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K52" s="3"/>
+      <c r="N52"/>
+      <c r="O52" s="4"/>
+      <c r="S52"/>
+      <c r="Y52"/>
+    </row>
+    <row r="53" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53"/>
       <c r="B53"/>
       <c r="C53"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-      <c r="M53" s="3"/>
-      <c r="P53"/>
-      <c r="Q53" s="4"/>
-      <c r="U53"/>
-      <c r="AA53"/>
-    </row>
-    <row r="54" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K53" s="3"/>
+      <c r="N53"/>
+      <c r="O53" s="4"/>
+      <c r="S53"/>
+      <c r="Y53"/>
+    </row>
+    <row r="54" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54"/>
       <c r="B54"/>
       <c r="C54"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
-      <c r="M54" s="3"/>
-      <c r="P54"/>
-      <c r="Q54" s="4"/>
-      <c r="U54"/>
-      <c r="AA54"/>
-    </row>
-    <row r="55" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K54" s="3"/>
+      <c r="N54"/>
+      <c r="O54" s="4"/>
+      <c r="S54"/>
+      <c r="Y54"/>
+    </row>
+    <row r="55" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55"/>
       <c r="B55"/>
       <c r="C55"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-      <c r="M55" s="3"/>
-      <c r="P55"/>
-      <c r="Q55" s="4"/>
-      <c r="U55"/>
-      <c r="AA55"/>
-    </row>
-    <row r="56" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K55" s="3"/>
+      <c r="N55"/>
+      <c r="O55" s="4"/>
+      <c r="S55"/>
+      <c r="Y55"/>
+    </row>
+    <row r="56" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56"/>
       <c r="B56"/>
       <c r="C56"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
-      <c r="M56" s="3"/>
-      <c r="P56"/>
-      <c r="Q56" s="4"/>
-      <c r="U56"/>
-      <c r="AA56"/>
-    </row>
-    <row r="57" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K56" s="3"/>
+      <c r="N56"/>
+      <c r="O56" s="4"/>
+      <c r="S56"/>
+      <c r="Y56"/>
+    </row>
+    <row r="57" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="B57"/>
       <c r="C57"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
-      <c r="M57" s="3"/>
-      <c r="P57"/>
-      <c r="Q57" s="4"/>
-      <c r="U57"/>
-      <c r="AA57"/>
-    </row>
-    <row r="58" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K57" s="3"/>
+      <c r="N57"/>
+      <c r="O57" s="4"/>
+      <c r="S57"/>
+      <c r="Y57"/>
+    </row>
+    <row r="58" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="B58"/>
       <c r="C58"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
-      <c r="M58" s="3"/>
-      <c r="P58"/>
-      <c r="Q58" s="4"/>
-      <c r="U58"/>
-      <c r="AA58"/>
-    </row>
-    <row r="59" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K58" s="3"/>
+      <c r="N58"/>
+      <c r="O58" s="4"/>
+      <c r="S58"/>
+      <c r="Y58"/>
+    </row>
+    <row r="59" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="B59"/>
       <c r="C59"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
-      <c r="M59" s="3"/>
-      <c r="P59"/>
-      <c r="Q59" s="4"/>
-      <c r="U59"/>
-      <c r="AA59"/>
-    </row>
-    <row r="60" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K59" s="3"/>
+      <c r="N59"/>
+      <c r="O59" s="4"/>
+      <c r="S59"/>
+      <c r="Y59"/>
+    </row>
+    <row r="60" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="B60"/>
       <c r="C60"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
-      <c r="K60" s="2"/>
-      <c r="M60" s="3"/>
-      <c r="P60"/>
-      <c r="Q60" s="4"/>
-      <c r="U60"/>
-      <c r="AA60"/>
-    </row>
-    <row r="61" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K60" s="3"/>
+      <c r="N60"/>
+      <c r="O60" s="4"/>
+      <c r="S60"/>
+      <c r="Y60"/>
+    </row>
+    <row r="61" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="B61"/>
       <c r="C61"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-      <c r="K61" s="2"/>
-      <c r="M61" s="3"/>
-      <c r="P61"/>
-      <c r="Q61" s="4"/>
-      <c r="U61"/>
-      <c r="AA61"/>
-    </row>
-    <row r="62" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K61" s="3"/>
+      <c r="N61"/>
+      <c r="O61" s="4"/>
+      <c r="S61"/>
+      <c r="Y61"/>
+    </row>
+    <row r="62" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62"/>
       <c r="B62"/>
       <c r="C62"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-      <c r="K62" s="2"/>
-      <c r="M62" s="3"/>
-      <c r="P62"/>
-      <c r="Q62" s="4"/>
-      <c r="U62"/>
-      <c r="AA62"/>
-    </row>
-    <row r="63" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K62" s="3"/>
+      <c r="N62"/>
+      <c r="O62" s="4"/>
+      <c r="S62"/>
+      <c r="Y62"/>
+    </row>
+    <row r="63" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="B63"/>
       <c r="C63"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
-      <c r="M63" s="3"/>
-      <c r="P63"/>
-      <c r="Q63" s="4"/>
-      <c r="U63"/>
-      <c r="AA63"/>
-    </row>
-    <row r="64" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K63" s="3"/>
+      <c r="N63"/>
+      <c r="O63" s="4"/>
+      <c r="S63"/>
+      <c r="Y63"/>
+    </row>
+    <row r="64" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="B64"/>
       <c r="C64"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
-      <c r="K64" s="2"/>
-      <c r="M64" s="3"/>
-      <c r="P64"/>
-      <c r="Q64" s="4"/>
-      <c r="U64"/>
-      <c r="AA64"/>
-    </row>
-    <row r="65" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K64" s="3"/>
+      <c r="N64"/>
+      <c r="O64" s="4"/>
+      <c r="S64"/>
+      <c r="Y64"/>
+    </row>
+    <row r="65" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65"/>
       <c r="B65"/>
       <c r="C65"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
-      <c r="M65" s="3"/>
-      <c r="P65"/>
-      <c r="Q65" s="4"/>
-      <c r="U65"/>
-      <c r="AA65"/>
-    </row>
-    <row r="66" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K65" s="3"/>
+      <c r="N65"/>
+      <c r="O65" s="4"/>
+      <c r="S65"/>
+      <c r="Y65"/>
+    </row>
+    <row r="66" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66"/>
       <c r="B66"/>
       <c r="C66"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
-      <c r="M66" s="3"/>
-      <c r="P66"/>
-      <c r="Q66" s="4"/>
-      <c r="U66"/>
-      <c r="AA66"/>
-    </row>
-    <row r="67" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K66" s="3"/>
+      <c r="N66"/>
+      <c r="O66" s="4"/>
+      <c r="S66"/>
+      <c r="Y66"/>
+    </row>
+    <row r="67" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67"/>
       <c r="B67"/>
       <c r="C67"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
-      <c r="M67" s="3"/>
-      <c r="P67"/>
-      <c r="Q67" s="4"/>
-      <c r="U67"/>
-      <c r="AA67"/>
-    </row>
-    <row r="68" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K67" s="3"/>
+      <c r="N67"/>
+      <c r="O67" s="4"/>
+      <c r="S67"/>
+      <c r="Y67"/>
+    </row>
+    <row r="68" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68"/>
       <c r="B68"/>
       <c r="C68"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
-      <c r="M68" s="3"/>
-      <c r="P68"/>
-      <c r="Q68" s="4"/>
-      <c r="U68"/>
-      <c r="AA68"/>
-    </row>
-    <row r="69" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K68" s="3"/>
+      <c r="N68"/>
+      <c r="O68" s="4"/>
+      <c r="S68"/>
+      <c r="Y68"/>
+    </row>
+    <row r="69" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="B69"/>
       <c r="C69"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
-      <c r="M69" s="3"/>
-      <c r="P69"/>
-      <c r="Q69" s="4"/>
-      <c r="U69"/>
-      <c r="AA69"/>
-    </row>
-    <row r="70" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K69" s="3"/>
+      <c r="N69"/>
+      <c r="O69" s="4"/>
+      <c r="S69"/>
+      <c r="Y69"/>
+    </row>
+    <row r="70" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70"/>
       <c r="B70"/>
       <c r="C70"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
-      <c r="K70" s="2"/>
-      <c r="M70" s="3"/>
-      <c r="P70"/>
-      <c r="Q70" s="4"/>
-      <c r="U70"/>
-      <c r="AA70"/>
-    </row>
-    <row r="71" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K70" s="3"/>
+      <c r="N70"/>
+      <c r="O70" s="4"/>
+      <c r="S70"/>
+      <c r="Y70"/>
+    </row>
+    <row r="71" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71"/>
       <c r="B71"/>
       <c r="C71"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-      <c r="K71" s="2"/>
-      <c r="M71" s="3"/>
-      <c r="P71"/>
-      <c r="Q71" s="4"/>
-      <c r="U71"/>
-      <c r="AA71"/>
-    </row>
-    <row r="72" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K71" s="3"/>
+      <c r="N71"/>
+      <c r="O71" s="4"/>
+      <c r="S71"/>
+      <c r="Y71"/>
+    </row>
+    <row r="72" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72"/>
       <c r="B72"/>
       <c r="C72"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
-      <c r="M72" s="3"/>
-      <c r="P72"/>
-      <c r="Q72" s="4"/>
-      <c r="U72"/>
-      <c r="AA72"/>
-    </row>
-    <row r="73" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K72" s="3"/>
+      <c r="N72"/>
+      <c r="O72" s="4"/>
+      <c r="S72"/>
+      <c r="Y72"/>
+    </row>
+    <row r="73" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73"/>
       <c r="B73"/>
       <c r="C73"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
-      <c r="K73" s="2"/>
-      <c r="M73" s="3"/>
-      <c r="P73"/>
-      <c r="Q73" s="4"/>
-      <c r="U73"/>
-      <c r="AA73"/>
-    </row>
-    <row r="74" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K73" s="3"/>
+      <c r="N73"/>
+      <c r="O73" s="4"/>
+      <c r="S73"/>
+      <c r="Y73"/>
+    </row>
+    <row r="74" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74"/>
       <c r="B74"/>
       <c r="C74"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
-      <c r="M74" s="3"/>
-      <c r="P74"/>
-      <c r="Q74" s="4"/>
-      <c r="U74"/>
-      <c r="AA74"/>
-    </row>
-    <row r="75" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K74" s="3"/>
+      <c r="N74"/>
+      <c r="O74" s="4"/>
+      <c r="S74"/>
+      <c r="Y74"/>
+    </row>
+    <row r="75" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75"/>
       <c r="B75"/>
       <c r="C75"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
-      <c r="M75" s="3"/>
-      <c r="P75"/>
-      <c r="Q75" s="4"/>
-      <c r="U75"/>
-      <c r="AA75"/>
-    </row>
-    <row r="76" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K75" s="3"/>
+      <c r="N75"/>
+      <c r="O75" s="4"/>
+      <c r="S75"/>
+      <c r="Y75"/>
+    </row>
+    <row r="76" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76"/>
       <c r="B76"/>
       <c r="C76"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
-      <c r="M76" s="3"/>
-      <c r="P76"/>
-      <c r="Q76" s="4"/>
-      <c r="U76"/>
-      <c r="AA76"/>
-    </row>
-    <row r="77" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K76" s="3"/>
+      <c r="N76"/>
+      <c r="O76" s="4"/>
+      <c r="S76"/>
+      <c r="Y76"/>
+    </row>
+    <row r="77" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77"/>
       <c r="B77"/>
       <c r="C77"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
-      <c r="M77" s="3"/>
-      <c r="P77"/>
-      <c r="Q77" s="4"/>
-      <c r="U77"/>
-      <c r="AA77"/>
-    </row>
-    <row r="78" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K77" s="3"/>
+      <c r="N77"/>
+      <c r="O77" s="4"/>
+      <c r="S77"/>
+      <c r="Y77"/>
+    </row>
+    <row r="78" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78"/>
       <c r="B78"/>
       <c r="C78"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
-      <c r="M78" s="3"/>
-      <c r="P78"/>
-      <c r="Q78" s="4"/>
-      <c r="U78"/>
-      <c r="AA78"/>
-    </row>
-    <row r="79" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K78" s="3"/>
+      <c r="N78"/>
+      <c r="O78" s="4"/>
+      <c r="S78"/>
+      <c r="Y78"/>
+    </row>
+    <row r="79" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79"/>
       <c r="B79"/>
       <c r="C79"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="2"/>
-      <c r="M79" s="3"/>
-      <c r="P79"/>
-      <c r="Q79" s="4"/>
-      <c r="U79"/>
-      <c r="AA79"/>
-    </row>
-    <row r="80" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K79" s="3"/>
+      <c r="N79"/>
+      <c r="O79" s="4"/>
+      <c r="S79"/>
+      <c r="Y79"/>
+    </row>
+    <row r="80" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80"/>
       <c r="B80"/>
       <c r="C80"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
-      <c r="M80" s="3"/>
-      <c r="P80"/>
-      <c r="Q80" s="4"/>
-      <c r="U80"/>
-      <c r="AA80"/>
-    </row>
-    <row r="81" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K80" s="3"/>
+      <c r="N80"/>
+      <c r="O80" s="4"/>
+      <c r="S80"/>
+      <c r="Y80"/>
+    </row>
+    <row r="81" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81"/>
       <c r="B81"/>
       <c r="C81"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="2"/>
-      <c r="M81" s="3"/>
-      <c r="P81"/>
-      <c r="Q81" s="4"/>
-      <c r="U81"/>
-      <c r="AA81"/>
-    </row>
-    <row r="82" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K81" s="3"/>
+      <c r="N81"/>
+      <c r="O81" s="4"/>
+      <c r="S81"/>
+      <c r="Y81"/>
+    </row>
+    <row r="82" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82"/>
       <c r="B82"/>
       <c r="C82"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
-      <c r="M82" s="3"/>
-      <c r="P82"/>
-      <c r="Q82" s="4"/>
-      <c r="U82"/>
-      <c r="AA82"/>
-    </row>
-    <row r="83" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K82" s="3"/>
+      <c r="N82"/>
+      <c r="O82" s="4"/>
+      <c r="S82"/>
+      <c r="Y82"/>
+    </row>
+    <row r="83" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83"/>
       <c r="B83"/>
       <c r="C83"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
-      <c r="K83" s="2"/>
-      <c r="M83" s="3"/>
-      <c r="P83"/>
-      <c r="Q83" s="4"/>
-      <c r="U83"/>
-      <c r="AA83"/>
-    </row>
-    <row r="84" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K83" s="3"/>
+      <c r="N83"/>
+      <c r="O83" s="4"/>
+      <c r="S83"/>
+      <c r="Y83"/>
+    </row>
+    <row r="84" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84"/>
       <c r="B84"/>
       <c r="C84"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="2"/>
-      <c r="M84" s="3"/>
-      <c r="P84"/>
-      <c r="Q84" s="4"/>
-      <c r="U84"/>
-      <c r="AA84"/>
-    </row>
-    <row r="85" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K84" s="3"/>
+      <c r="N84"/>
+      <c r="O84" s="4"/>
+      <c r="S84"/>
+      <c r="Y84"/>
+    </row>
+    <row r="85" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85"/>
       <c r="B85"/>
       <c r="C85"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
-      <c r="J85" s="2"/>
-      <c r="K85" s="2"/>
-      <c r="M85" s="3"/>
-      <c r="P85"/>
-      <c r="Q85" s="4"/>
-      <c r="U85"/>
-      <c r="AA85"/>
-    </row>
-    <row r="86" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K85" s="3"/>
+      <c r="N85"/>
+      <c r="O85" s="4"/>
+      <c r="S85"/>
+      <c r="Y85"/>
+    </row>
+    <row r="86" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86"/>
       <c r="B86"/>
       <c r="C86"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
-      <c r="J86" s="2"/>
-      <c r="K86" s="2"/>
-      <c r="M86" s="3"/>
-      <c r="P86"/>
-      <c r="Q86" s="4"/>
-      <c r="U86"/>
-      <c r="AA86"/>
-    </row>
-    <row r="87" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K86" s="3"/>
+      <c r="N86"/>
+      <c r="O86" s="4"/>
+      <c r="S86"/>
+      <c r="Y86"/>
+    </row>
+    <row r="87" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87"/>
       <c r="B87"/>
       <c r="C87"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="2"/>
-      <c r="M87" s="3"/>
-      <c r="P87"/>
-      <c r="Q87" s="4"/>
-      <c r="U87"/>
-      <c r="AA87"/>
-    </row>
-    <row r="88" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K87" s="3"/>
+      <c r="N87"/>
+      <c r="O87" s="4"/>
+      <c r="S87"/>
+      <c r="Y87"/>
+    </row>
+    <row r="88" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88"/>
       <c r="B88"/>
       <c r="C88"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
-      <c r="K88" s="2"/>
-      <c r="M88" s="3"/>
-      <c r="P88"/>
-      <c r="Q88" s="4"/>
-      <c r="U88"/>
-      <c r="AA88"/>
-    </row>
-    <row r="89" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K88" s="3"/>
+      <c r="N88"/>
+      <c r="O88" s="4"/>
+      <c r="S88"/>
+      <c r="Y88"/>
+    </row>
+    <row r="89" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89"/>
       <c r="B89"/>
       <c r="C89"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
-      <c r="K89" s="2"/>
-      <c r="M89" s="3"/>
-      <c r="P89"/>
-      <c r="Q89" s="4"/>
-      <c r="U89"/>
-      <c r="AA89"/>
-    </row>
-    <row r="90" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K89" s="3"/>
+      <c r="N89"/>
+      <c r="O89" s="4"/>
+      <c r="S89"/>
+      <c r="Y89"/>
+    </row>
+    <row r="90" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90"/>
       <c r="B90"/>
       <c r="C90"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
-      <c r="M90" s="3"/>
-      <c r="P90"/>
-      <c r="Q90" s="4"/>
-      <c r="U90"/>
-      <c r="AA90"/>
-    </row>
-    <row r="91" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K90" s="3"/>
+      <c r="N90"/>
+      <c r="O90" s="4"/>
+      <c r="S90"/>
+      <c r="Y90"/>
+    </row>
+    <row r="91" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91"/>
       <c r="B91"/>
       <c r="C91"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
-      <c r="J91" s="2"/>
-      <c r="K91" s="2"/>
-      <c r="M91" s="3"/>
-      <c r="P91"/>
-      <c r="Q91" s="4"/>
-      <c r="U91"/>
-      <c r="AA91"/>
-    </row>
-    <row r="92" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K91" s="3"/>
+      <c r="N91"/>
+      <c r="O91" s="4"/>
+      <c r="S91"/>
+      <c r="Y91"/>
+    </row>
+    <row r="92" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92"/>
       <c r="B92"/>
       <c r="C92"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
-      <c r="K92" s="2"/>
-      <c r="M92" s="3"/>
-      <c r="P92"/>
-      <c r="Q92" s="4"/>
-      <c r="U92"/>
-      <c r="AA92"/>
-    </row>
-    <row r="93" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K92" s="3"/>
+      <c r="N92"/>
+      <c r="O92" s="4"/>
+      <c r="S92"/>
+      <c r="Y92"/>
+    </row>
+    <row r="93" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93"/>
       <c r="B93"/>
       <c r="C93"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
-      <c r="J93" s="2"/>
-      <c r="K93" s="2"/>
-      <c r="M93" s="3"/>
-      <c r="P93"/>
-      <c r="Q93" s="4"/>
-      <c r="U93"/>
-      <c r="AA93"/>
-    </row>
-    <row r="94" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K93" s="3"/>
+      <c r="N93"/>
+      <c r="O93" s="4"/>
+      <c r="S93"/>
+      <c r="Y93"/>
+    </row>
+    <row r="94" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94"/>
       <c r="B94"/>
       <c r="C94"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
-      <c r="J94" s="2"/>
-      <c r="K94" s="2"/>
-      <c r="M94" s="3"/>
-      <c r="P94"/>
-      <c r="Q94" s="4"/>
-      <c r="U94"/>
-      <c r="AA94"/>
-    </row>
-    <row r="95" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K94" s="3"/>
+      <c r="N94"/>
+      <c r="O94" s="4"/>
+      <c r="S94"/>
+      <c r="Y94"/>
+    </row>
+    <row r="95" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95"/>
       <c r="B95"/>
       <c r="C95"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
-      <c r="J95" s="2"/>
-      <c r="K95" s="2"/>
-      <c r="M95" s="3"/>
-      <c r="P95"/>
-      <c r="Q95" s="4"/>
-      <c r="U95"/>
-      <c r="AA95"/>
-    </row>
-    <row r="96" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K95" s="3"/>
+      <c r="N95"/>
+      <c r="O95" s="4"/>
+      <c r="S95"/>
+      <c r="Y95"/>
+    </row>
+    <row r="96" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96"/>
       <c r="B96"/>
       <c r="C96"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
-      <c r="J96" s="2"/>
-      <c r="K96" s="2"/>
-      <c r="M96" s="3"/>
-      <c r="P96"/>
-      <c r="Q96" s="4"/>
-      <c r="U96"/>
-      <c r="AA96"/>
-    </row>
-    <row r="97" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K96" s="3"/>
+      <c r="N96"/>
+      <c r="O96" s="4"/>
+      <c r="S96"/>
+      <c r="Y96"/>
+    </row>
+    <row r="97" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97"/>
       <c r="B97"/>
       <c r="C97"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
-      <c r="J97" s="2"/>
-      <c r="K97" s="2"/>
-      <c r="M97" s="3"/>
-      <c r="P97"/>
-      <c r="Q97" s="4"/>
-      <c r="U97"/>
-      <c r="AA97"/>
-    </row>
-    <row r="98" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K97" s="3"/>
+      <c r="N97"/>
+      <c r="O97" s="4"/>
+      <c r="S97"/>
+      <c r="Y97"/>
+    </row>
+    <row r="98" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98"/>
       <c r="B98"/>
       <c r="C98"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
-      <c r="J98" s="2"/>
-      <c r="K98" s="2"/>
-      <c r="M98" s="3"/>
-      <c r="P98"/>
-      <c r="Q98" s="4"/>
-      <c r="U98"/>
-      <c r="AA98"/>
-    </row>
-    <row r="99" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K98" s="3"/>
+      <c r="N98"/>
+      <c r="O98" s="4"/>
+      <c r="S98"/>
+      <c r="Y98"/>
+    </row>
+    <row r="99" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99"/>
       <c r="B99"/>
       <c r="C99"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
-      <c r="J99" s="2"/>
-      <c r="K99" s="2"/>
-      <c r="M99" s="3"/>
-      <c r="P99"/>
-      <c r="Q99" s="4"/>
-      <c r="U99"/>
-      <c r="AA99"/>
-    </row>
-    <row r="100" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K99" s="3"/>
+      <c r="N99"/>
+      <c r="O99" s="4"/>
+      <c r="S99"/>
+      <c r="Y99"/>
+    </row>
+    <row r="100" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100"/>
       <c r="B100"/>
       <c r="C100"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
-      <c r="J100" s="2"/>
-      <c r="K100" s="2"/>
-      <c r="M100" s="3"/>
-      <c r="P100"/>
-      <c r="Q100" s="4"/>
-      <c r="U100"/>
-      <c r="AA100"/>
-    </row>
-    <row r="101" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K100" s="3"/>
+      <c r="N100"/>
+      <c r="O100" s="4"/>
+      <c r="S100"/>
+      <c r="Y100"/>
+    </row>
+    <row r="101" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101"/>
       <c r="B101"/>
       <c r="C101"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
-      <c r="J101" s="2"/>
-      <c r="K101" s="2"/>
-      <c r="M101" s="3"/>
-      <c r="P101"/>
-      <c r="Q101" s="4"/>
-      <c r="U101"/>
-      <c r="AA101"/>
-    </row>
-    <row r="102" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K101" s="3"/>
+      <c r="N101"/>
+      <c r="O101" s="4"/>
+      <c r="S101"/>
+      <c r="Y101"/>
+    </row>
+    <row r="102" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102"/>
       <c r="B102"/>
       <c r="C102"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
-      <c r="J102" s="2"/>
-      <c r="K102" s="2"/>
-      <c r="M102" s="3"/>
-      <c r="P102"/>
-      <c r="Q102" s="4"/>
-      <c r="U102"/>
-      <c r="AA102"/>
-    </row>
-    <row r="103" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K102" s="3"/>
+      <c r="N102"/>
+      <c r="O102" s="4"/>
+      <c r="S102"/>
+      <c r="Y102"/>
+    </row>
+    <row r="103" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
       <c r="B103"/>
       <c r="C103"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
-      <c r="J103" s="2"/>
-      <c r="K103" s="2"/>
-      <c r="M103" s="3"/>
-      <c r="P103"/>
-      <c r="Q103" s="4"/>
-      <c r="U103"/>
-      <c r="AA103"/>
-    </row>
-    <row r="104" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K103" s="3"/>
+      <c r="N103"/>
+      <c r="O103" s="4"/>
+      <c r="S103"/>
+      <c r="Y103"/>
+    </row>
+    <row r="104" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104"/>
       <c r="B104"/>
       <c r="C104"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
-      <c r="J104" s="2"/>
-      <c r="K104" s="2"/>
-      <c r="M104" s="3"/>
-      <c r="P104"/>
-      <c r="Q104" s="4"/>
-      <c r="U104"/>
-      <c r="AA104"/>
-    </row>
-    <row r="105" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K104" s="3"/>
+      <c r="N104"/>
+      <c r="O104" s="4"/>
+      <c r="S104"/>
+      <c r="Y104"/>
+    </row>
+    <row r="105" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105"/>
       <c r="B105"/>
       <c r="C105"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
-      <c r="J105" s="2"/>
-      <c r="K105" s="2"/>
-      <c r="M105" s="3"/>
-      <c r="P105"/>
-      <c r="Q105" s="4"/>
-      <c r="U105"/>
-      <c r="AA105"/>
-    </row>
-    <row r="106" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K105" s="3"/>
+      <c r="N105"/>
+      <c r="O105" s="4"/>
+      <c r="S105"/>
+      <c r="Y105"/>
+    </row>
+    <row r="106" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106"/>
       <c r="B106"/>
       <c r="C106"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
       <c r="H106" s="2"/>
       <c r="I106" s="2"/>
-      <c r="J106" s="2"/>
-      <c r="K106" s="2"/>
-      <c r="M106" s="3"/>
-      <c r="P106"/>
-      <c r="Q106" s="4"/>
-      <c r="U106"/>
-      <c r="AA106"/>
-    </row>
-    <row r="107" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K106" s="3"/>
+      <c r="N106"/>
+      <c r="O106" s="4"/>
+      <c r="S106"/>
+      <c r="Y106"/>
+    </row>
+    <row r="107" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107"/>
       <c r="B107"/>
       <c r="C107"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
       <c r="H107" s="2"/>
       <c r="I107" s="2"/>
-      <c r="J107" s="2"/>
-      <c r="K107" s="2"/>
-      <c r="M107" s="3"/>
-      <c r="P107"/>
-      <c r="Q107" s="4"/>
-      <c r="U107"/>
-      <c r="AA107"/>
-    </row>
-    <row r="108" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K107" s="3"/>
+      <c r="N107"/>
+      <c r="O107" s="4"/>
+      <c r="S107"/>
+      <c r="Y107"/>
+    </row>
+    <row r="108" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108"/>
       <c r="B108"/>
       <c r="C108"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
       <c r="H108" s="2"/>
       <c r="I108" s="2"/>
-      <c r="J108" s="2"/>
-      <c r="K108" s="2"/>
-      <c r="M108" s="3"/>
-      <c r="P108"/>
-      <c r="Q108" s="4"/>
-      <c r="U108"/>
-      <c r="AA108"/>
+      <c r="K108" s="3"/>
+      <c r="N108"/>
+      <c r="O108" s="4"/>
+      <c r="S108"/>
+      <c r="Y108"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="5">
-    <mergeCell ref="C2:L2"/>
-    <mergeCell ref="G3:L3"/>
+    <mergeCell ref="C2:J2"/>
+    <mergeCell ref="E3:J3"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="G4:L4"/>
-    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="A5:J5"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="M10 M7 M11:M12" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="1">
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="K10 K6 K11:K12" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="91" firstPageNumber="0" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" firstPageNumber="0" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/owlcms/src/main/resources/templates/teams/VFE_Teams-A4.xlsx
+++ b/owlcms/src/main/resources/templates/teams/VFE_Teams-A4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms4\owlcms\src\main\resources\templates\teams\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84B9889-3FDD-4A92-ABE6-B31D6032E8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBDAE707-CD3C-434A-81CB-E2FD1815BE20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6000" yWindow="3300" windowWidth="22410" windowHeight="15555" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6345" yWindow="3645" windowWidth="22410" windowHeight="15555" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team List" sheetId="3" r:id="rId1"/>
@@ -545,6 +545,9 @@
     <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -557,9 +560,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1007,16 +1007,16 @@
       <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
       <c r="L2" s="4"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -1037,14 +1037,14 @@
         <v>4</v>
       </c>
       <c r="D3" s="6"/>
-      <c r="E3" s="46" t="s">
+      <c r="E3" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
       <c r="L3" s="4"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -1065,14 +1065,14 @@
         <v>7</v>
       </c>
       <c r="D4" s="8"/>
-      <c r="E4" s="48" t="s">
+      <c r="E4" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
       <c r="L4" s="4"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -1083,18 +1083,18 @@
       <c r="X4"/>
     </row>
     <row r="5" spans="1:24" s="9" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
       <c r="K5" s="10"/>
       <c r="L5" s="11"/>
       <c r="M5" s="12"/>
@@ -1331,11 +1331,11 @@
       <c r="M15" s="19"/>
     </row>
     <row r="16" spans="1:24" s="20" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="47" t="s">
+      <c r="A16" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
       <c r="D16" s="35"/>
       <c r="E16" s="36"/>
       <c r="F16" s="17"/>
@@ -2615,12 +2615,11 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="C2:J2"/>
     <mergeCell ref="E3:J3"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="E4:J4"/>
-    <mergeCell ref="A5:J5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="K10 K6 K11:K12" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/owlcms/src/main/resources/templates/teams/VFE_Teams-A4.xlsx
+++ b/owlcms/src/main/resources/templates/teams/VFE_Teams-A4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms4\owlcms\src\main\resources\templates\teams\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBDAE707-CD3C-434A-81CB-E2FD1815BE20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F1214F-FA9B-48AD-BBB1-D82E6BCB23A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6345" yWindow="3645" windowWidth="22410" windowHeight="15555" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6000" yWindow="3300" windowWidth="22410" windowHeight="15555" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team List" sheetId="3" r:id="rId1"/>
@@ -47,7 +47,6 @@
     <definedName name="P_C_">#REF!</definedName>
     <definedName name="PeséeGroupFilter">#REF!</definedName>
     <definedName name="PRÉNOM">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Team List'!$A:$F</definedName>
     <definedName name="progr_">#REF!</definedName>
     <definedName name="requestedCJ">#REF!</definedName>
     <definedName name="StartGroupFilter">#REF!</definedName>
@@ -943,8 +942,8 @@
     <col min="2" max="2" width="8.5703125" customWidth="1"/>
     <col min="3" max="3" width="30.5703125" customWidth="1"/>
     <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="1" customWidth="1"/>
-    <col min="6" max="9" width="11.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" style="1" customWidth="1"/>
+    <col min="6" max="9" width="13.7109375" style="2" customWidth="1"/>
     <col min="10" max="10" width="23.85546875" style="1" customWidth="1"/>
     <col min="11" max="11" width="16.28515625" style="3" customWidth="1"/>
     <col min="12" max="13" width="7.7109375" style="1" customWidth="1"/>
@@ -2629,7 +2628,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" firstPageNumber="0" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="53" firstPageNumber="0" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
